--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -8297,7 +8297,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -20482,7 +20482,7 @@
           <t>C | 546呎 (2房)
 $1,611万
 $29,500/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -21062,7 +21062,7 @@
           <t>E | 499呎 (2房)
 $1,391万
 $27,878/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -21093,7 +21093,7 @@
           <t>C | 546呎 (2房)
 $1,529万
 $28,011/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1C座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9367,7 +9229,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9413,7 +9275,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9459,7 +9321,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -10352,19 +10214,19 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>16706000</v>
+        <v>13699000</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>34517</v>
+        <v>28304</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -11071,7 +10933,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -11496,19 +11358,19 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
-        <v>16762100</v>
+        <v>13745000</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>33591</v>
+        <v>27545</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
@@ -18615,4031 +18477,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海盈山第4B期 - 1A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>36 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2291呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 2020呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$7,367万
-$48,630/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$5,625万
-$48,745/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$7,367万
-$48,630/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$5,625万
-$48,745/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$6,832万
-$45,098/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$5,372万
-$46,553/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$6,785万
-$44,787/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$5,335万
-$46,231/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$6,801万
-$44,890/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$5,335万
-$46,231/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$6,600万
-$43,562/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$5,189万
-$44,967/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$6,554万
-$43,260/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$5,153万
-$44,657/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 1450呎 (4+房)
-$6,955万
-$47,968/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 1450呎 (4+房)
-$6,631万
-$45,728/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 1450呎 (4+房)
-$6,419万
-$44,267/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$6,374万
-$42,074/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$5,012万
-$43,434/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-$6,330万
-$41,783/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 1154呎 (4+房)
-$4,978万
-$43,134/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1515呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1517呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 1517呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 1517呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 1517呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 1517呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 1517呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 1517呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 1517呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 1450呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 1148呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海盈山第4B期 - 1B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>167 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>43 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>56 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1740呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1052呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr"/>
-      <c r="E6" s="19" t="inlineStr"/>
-      <c r="F6" s="19" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 956呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 965呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 956呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 965呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 956呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 965呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 956呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 965呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 956呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 965呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,733万
-$31,747/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,864万
-$38,503/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,908万
-$38,230/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,726万
-$31,621/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,856万
-$38,349/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,900万
-$38,076/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$4,234万
-$44,102/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$4,196万
-$43,709/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$2,097万
-$38,408/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,516万
-$31,322/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,892万
-$37,922/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$4,205万
-$43,798/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$4,167万
-$43,406/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$2,089万
-$38,254/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,510万
-$31,196/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,885万
-$37,771/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$2,080万
-$38,102/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,834万
-$37,890/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,877万
-$37,621/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,969万
-$41,342/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3,934万
-$40,974/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$2,072万
-$37,950/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,827万
-$37,742/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,870万
-$37,472/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$4,099万
-$42,698/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3,906万
-$40,691/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$2,064万
-$37,798/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,820万
-$37,593/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,862万
-$37,321/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,941万
-$41,055/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3,906万
-$40,691/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$2,064万
-$37,798/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,820万
-$37,593/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,862万
-$37,321/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,624万
-$29,736/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,745万
-$36,061/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,787万
-$35,806/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,834万
-$39,933/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3,800万
-$39,579/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,617万
-$29,617/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,738万
-$35,918/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,780万
-$35,662/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,807万
-$39,657/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3,773万
-$39,306/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,611万
-$29,500/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,732万
-$35,776/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,772万
-$35,520/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,874万
-$40,351/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,604万
-$29,383/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,725万
-$35,635/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,765万
-$35,378/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,847万
-$40,070/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,598万
-$29,264/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,409万
-$29,103/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,442万
-$28,894/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,878万
-$40,395/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3,844万
-$40,036/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,669万
-$30,570/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,711万
-$35,351/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,751万
-$35,097/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3,670万
-$38,230/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,663万
-$30,449/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,704万
-$35,210/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,744万
-$34,958/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3,703万
-$38,573/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3,823万
-$39,824/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,585万
-$29,033/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,397万
-$28,872/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,430万
-$28,665/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,573万
-$28,802/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,386万
-$28,643/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,731万
-$34,681/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,566万
-$28,687/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,381万
-$28,529/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,413万
-$28,325/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,560万
-$28,571/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,375万
-$28,415/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,717万
-$34,403/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,554万
-$28,460/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,671万
-$34,517/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,710万
-$34,269/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,623万
-$29,729/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,364万
-$28,190/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,703万
-$34,132/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,542万
-$28,233/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,425万
-$29,446/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,696万
-$33,997/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,542万
-$28,233/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,359万
-$28,076/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,391万
-$27,878/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,529万
-$28,011/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,348万
-$27,853/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,683万
-$33,726/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1,523万
-$27,897/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1,343万
-$27,742/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1,676万
-$33,591/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 911呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>C | 508呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>E | 461呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海盈山第4B期 - 1C座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>133 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>133 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1054呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr"/>
-      <c r="D6" s="19" t="inlineStr"/>
-      <c r="E6" s="19" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 859呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 857呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 857呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 857呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 857呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 857呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 857呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 857呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 857呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>D | 592呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 812呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 551呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>C | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 554呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1C座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +144,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +225,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -18477,4 +18658,4031 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2291呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 2020呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$7367万
+$48,630/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$5625万
+$48,745/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$7367万
+$48,630/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$5625万
+$48,745/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$6832万
+$45,098/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$5372万
+$46,553/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$6785万
+$44,787/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$5335万
+$46,231/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$6801万
+$44,890/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$5335万
+$46,231/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$6600万
+$43,562/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$5189万
+$44,967/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$6554万
+$43,260/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$5153万
+$44,657/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1450呎 (4+房)
+$6955万
+$47,968/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 1450呎 (4+房)
+$6631万
+$45,728/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 1450呎 (4+房)
+$6419万
+$44,267/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$6374万
+$42,074/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$5012万
+$43,434/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+$6330万
+$41,783/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 1154呎 (4+房)
+$4978万
+$43,134/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1515呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1517呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1517呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 1517呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 1517呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>A | 1517呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 1517呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 1517呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 1517呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 1450呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 1148呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1740呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1052呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr"/>
+      <c r="F5" s="23" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 956呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 965呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 956呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 965呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 956呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 965呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 956呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 965呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 956呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 965呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1733万
+$31,747/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1864万
+$38,503/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1908万
+$38,230/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1726万
+$31,621/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1856万
+$38,349/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1900万
+$38,076/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$4234万
+$44,102/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$4196万
+$43,709/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$2097万
+$38,408/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1516万
+$31,322/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1892万
+$37,922/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$4205万
+$43,798/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$4167万
+$43,406/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$2089万
+$38,254/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1510万
+$31,196/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1885万
+$37,771/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$2080万
+$38,102/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1834万
+$37,890/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1877万
+$37,621/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3969万
+$41,342/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3934万
+$40,974/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$2072万
+$37,950/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1827万
+$37,742/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1870万
+$37,472/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$4099万
+$42,698/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3906万
+$40,691/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$2064万
+$37,798/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1820万
+$37,593/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1862万
+$37,321/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3941万
+$41,055/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3906万
+$40,691/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$2064万
+$37,798/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1820万
+$37,593/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1862万
+$37,321/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1624万
+$29,736/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1745万
+$36,061/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1787万
+$35,806/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3834万
+$39,933/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3800万
+$39,579/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1617万
+$29,617/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1738万
+$35,918/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1780万
+$35,662/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3807万
+$39,657/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3773万
+$39,306/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1611万
+$29,500/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1732万
+$35,776/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1772万
+$35,520/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3874万
+$40,351/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1604万
+$29,383/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1725万
+$35,635/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1765万
+$35,378/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3847万
+$40,070/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1598万
+$29,264/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1409万
+$29,103/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1442万
+$28,894/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3878万
+$40,395/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3844万
+$40,036/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1669万
+$30,570/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1711万
+$35,351/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1751万
+$35,097/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3670万
+$38,230/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1663万
+$30,449/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1704万
+$35,210/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1744万
+$34,958/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3703万
+$38,573/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3823万
+$39,824/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1585万
+$29,033/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1397万
+$28,872/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1430万
+$28,665/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1573万
+$28,802/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1386万
+$28,643/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1731万
+$34,681/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1566万
+$28,687/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1381万
+$28,529/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1413万
+$28,325/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1560万
+$28,571/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1375万
+$28,415/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1717万
+$34,403/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1554万
+$28,460/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1370万
+$28,304/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1710万
+$34,269/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1623万
+$29,729/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1364万
+$28,190/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1703万
+$34,132/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1542万
+$28,233/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1425万
+$29,446/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1696万
+$33,997/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1542万
+$28,233/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1359万
+$28,076/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1391万
+$27,878/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1529万
+$28,011/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1348万
+$27,853/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1683万
+$33,726/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1523万
+$27,897/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1343万
+$27,742/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1374万
+$27,545/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 911呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 508呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 461呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1C座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1054呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr"/>
+      <c r="D5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 859呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 857呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 592呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 812呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 551呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 554呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -20008,7 +20008,7 @@
           <t>C | 546呎 (2房)
 $1733万
 $31,747/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -20603,7 +20603,7 @@
           <t>A | 960呎 (3房)
 $3847万
 $40,070/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -20752,7 +20752,7 @@
           <t>B | 960呎 (3房)
 $3823万
 $39,824/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -20901,7 +20901,7 @@
           <t>C | 546呎 (2房)
 $1560万
 $28,571/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -20948,7 +20948,7 @@
           <t>C | 546呎 (2房)
 $1554万
 $28,460/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -10608,7 +10608,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -27339,7 +27339,7 @@
           <t>C | 546呎 (2房)
 $1624万
 $29,736/呎
-(26年-06月-17日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -27715,7 +27715,7 @@
           <t>C | 546呎 (2房)
 $1573万
 $28,802/呎
-(26年-06月-17日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12991,34 +12991,34 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>17306000</v>
+        <v>14191000</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>34681</v>
+        <v>28439</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K188" s="5" t="n">
-        <v>14190920</v>
+        <v>14191000</v>
       </c>
       <c r="L188" s="5" t="n">
         <v>28439</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N188" s="3" t="inlineStr">
@@ -13643,34 +13643,34 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>17167000</v>
+        <v>14077000</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>34403</v>
+        <v>28210</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>14076940</v>
+        <v>14077000</v>
       </c>
       <c r="L198" s="5" t="n">
         <v>28210</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14621,34 +14621,34 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
-        <v>16964600</v>
+        <v>13911000</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>33997</v>
+        <v>27878</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>13910972</v>
+        <v>13911000</v>
       </c>
       <c r="L213" s="5" t="n">
         <v>27878</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -26525,7 +26525,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26963,7 +26963,7 @@
           <t>C | 546呎 (2房)
 $1726万
 $31,621/呎
-(26年-06月-17日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -27018,7 +27018,7 @@
           <t>D | 484呎 (2房)
 $1516万
 $31,322/呎
-(26年-06月-17日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -27065,7 +27065,7 @@
           <t>D | 484呎 (2房)
 $1510万
 $31,196/呎
-(26年-06月-17日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -27386,7 +27386,7 @@
           <t>C | 546呎 (2房)
 $1617万
 $29,617/呎
-(26年-06月-21日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -27527,7 +27527,7 @@
           <t>C | 546呎 (2房)
 $1598万
 $29,264/呎
-(26年-06月-17日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -27535,7 +27535,7 @@
           <t>D | 484呎 (2房)
 $1409万
 $29,103/呎
-(26年-06月-17日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -27543,7 +27543,7 @@
           <t>E | 499呎 (2房)
 $1442万
 $28,894/呎
-(26年-06月-17日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -27574,7 +27574,7 @@
           <t>C | 546呎 (2房)
 $1669万
 $30,570/呎
-(26年-06月-17日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -27621,7 +27621,7 @@
           <t>C | 546呎 (2房)
 $1663万
 $30,449/呎
-(26年-06月-17日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -27726,12 +27726,12 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-$1731万
-$34,681/呎
-(在售)</t>
+$1419万
+$28,439/呎
+(26年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -27817,15 +27817,15 @@
           <t>D | 484呎 (2房)
 $1375万
 $28,415/呎
-(26年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-$1717万
-$34,403/呎
-(在售)</t>
+$1408万
+$28,210/呎
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
           <t>C | 546呎 (2房)
 $1623万
 $29,729/呎
-(26年-06月-17日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -27961,12 +27961,12 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-$1696万
-$33,997/呎
-(在售)</t>
+$1391万
+$27,878/呎
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -28052,7 +28052,7 @@
           <t>D | 484呎 (2房)
 $1348万
 $27,853/呎
-(26年-06月-28日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -28091,7 +28091,7 @@
           <t>C | 546呎 (2房)
 $1523万
 $27,897/呎
-(26年-06月-18日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -28099,7 +28099,7 @@
           <t>D | 484呎 (2房)
 $1343万
 $27,742/呎
-(26年-06月-22日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -25888,7 +25888,7 @@
           <t>A | 1515呎 (4+房)
 $7367万
 $48,630/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25896,7 +25896,7 @@
           <t>B | 1154呎 (4+房)
 $5625万
 $48,745/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -25911,7 +25911,7 @@
           <t>A | 1515呎 (4+房)
 $7367万
 $48,630/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25919,7 +25919,7 @@
           <t>B | 1154呎 (4+房)
 $5625万
 $48,745/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -25957,7 +25957,7 @@
           <t>A | 1515呎 (4+房)
 $6832万
 $45,098/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25965,7 +25965,7 @@
           <t>B | 1154呎 (4+房)
 $5372万
 $46,553/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -25980,7 +25980,7 @@
           <t>A | 1515呎 (4+房)
 $6785万
 $44,787/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25988,7 +25988,7 @@
           <t>B | 1154呎 (4+房)
 $5335万
 $46,231/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26003,7 +26003,7 @@
           <t>A | 1515呎 (4+房)
 $6801万
 $44,890/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26011,7 +26011,7 @@
           <t>B | 1154呎 (4+房)
 $5335万
 $46,231/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26072,7 +26072,7 @@
           <t>A | 1515呎 (4+房)
 $6600万
 $43,562/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -26080,7 +26080,7 @@
           <t>B | 1154呎 (4+房)
 $5189万
 $44,967/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26095,7 +26095,7 @@
           <t>A | 1515呎 (4+房)
 $6554万
 $43,260/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -26103,7 +26103,7 @@
           <t>B | 1154呎 (4+房)
 $5153万
 $44,657/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26118,7 +26118,7 @@
           <t>A | 1450呎 (4+房)
 $6955万
 $47,968/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>A | 1450呎 (4+房)
 $6631万
 $45,728/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -26164,7 +26164,7 @@
           <t>A | 1450呎 (4+房)
 $6419万
 $44,267/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -26187,7 +26187,7 @@
           <t>A | 1515呎 (4+房)
 $6374万
 $42,074/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -26195,7 +26195,7 @@
           <t>B | 1154呎 (4+房)
 $5012万
 $43,434/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26210,7 +26210,7 @@
           <t>A | 1515呎 (4+房)
 $6330万
 $41,783/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -26218,7 +26218,7 @@
           <t>B | 1154呎 (4+房)
 $4978万
 $43,134/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -26916,7 +26916,7 @@
           <t>C | 546呎 (2房)
 $1733万
 $31,747/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -26963,7 +26963,7 @@
           <t>C | 546呎 (2房)
 $1726万
 $31,621/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -26994,7 +26994,7 @@
           <t>A | 960呎 (3房)
 $4234万
 $44,102/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -27002,7 +27002,7 @@
           <t>B | 960呎 (3房)
 $4196万
 $43,709/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -27018,7 +27018,7 @@
           <t>D | 484呎 (2房)
 $1516万
 $31,322/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -27041,7 +27041,7 @@
           <t>A | 960呎 (3房)
 $4205万
 $43,798/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -27049,7 +27049,7 @@
           <t>B | 960呎 (3房)
 $4167万
 $43,406/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -27065,7 +27065,7 @@
           <t>D | 484呎 (2房)
 $1510万
 $31,196/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -27135,7 +27135,7 @@
           <t>A | 960呎 (3房)
 $3969万
 $41,342/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -27143,7 +27143,7 @@
           <t>B | 960呎 (3房)
 $3934万
 $40,974/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27182,7 +27182,7 @@
           <t>A | 960呎 (3房)
 $4099万
 $42,698/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -27190,7 +27190,7 @@
           <t>B | 960呎 (3房)
 $3906万
 $40,691/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -27229,7 +27229,7 @@
           <t>A | 960呎 (3房)
 $3941万
 $41,055/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -27237,7 +27237,7 @@
           <t>B | 960呎 (3房)
 $3906万
 $40,691/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -27339,7 +27339,7 @@
           <t>C | 546呎 (2房)
 $1624万
 $29,736/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -27370,7 +27370,7 @@
           <t>A | 960呎 (3房)
 $3834万
 $39,933/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -27378,7 +27378,7 @@
           <t>B | 960呎 (3房)
 $3800万
 $39,579/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -27386,7 +27386,7 @@
           <t>C | 546呎 (2房)
 $1617万
 $29,617/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -27417,7 +27417,7 @@
           <t>A | 960呎 (3房)
 $3807万
 $39,657/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -27425,7 +27425,7 @@
           <t>B | 960呎 (3房)
 $3773万
 $39,306/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -27433,7 +27433,7 @@
           <t>C | 546呎 (2房)
 $1611万
 $29,500/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -27464,7 +27464,7 @@
           <t>A | 960呎 (3房)
 $3874万
 $40,351/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -27480,7 +27480,7 @@
           <t>C | 546呎 (2房)
 $1604万
 $29,383/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -27511,7 +27511,7 @@
           <t>A | 960呎 (3房)
 $3847万
 $40,070/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -27519,7 +27519,7 @@
           <t>B | 960呎 (3房)
 $3813万
 $39,715/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -27527,7 +27527,7 @@
           <t>C | 546呎 (2房)
 $1598万
 $29,264/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -27535,7 +27535,7 @@
           <t>D | 484呎 (2房)
 $1409万
 $29,103/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -27543,7 +27543,7 @@
           <t>E | 499呎 (2房)
 $1442万
 $28,894/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27558,7 @@
           <t>A | 960呎 (3房)
 $3878万
 $40,395/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -27566,7 +27566,7 @@
           <t>B | 960呎 (3房)
 $3844万
 $40,036/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -27574,7 +27574,7 @@
           <t>C | 546呎 (2房)
 $1669万
 $30,570/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -27613,7 +27613,7 @@
           <t>B | 960呎 (3房)
 $3670万
 $38,230/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -27621,7 +27621,7 @@
           <t>C | 546呎 (2房)
 $1663万
 $30,449/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -27652,7 +27652,7 @@
           <t>A | 960呎 (3房)
 $3703万
 $38,573/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -27660,7 +27660,7 @@
           <t>B | 960呎 (3房)
 $3823万
 $39,824/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -27668,7 +27668,7 @@
           <t>C | 546呎 (2房)
 $1585万
 $29,033/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -27676,7 +27676,7 @@
           <t>D | 484呎 (2房)
 $1397万
 $28,872/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -27684,7 +27684,7 @@
           <t>E | 499呎 (2房)
 $1430万
 $28,665/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27715,7 @@
           <t>C | 546呎 (2房)
 $1573万
 $28,802/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -27723,7 +27723,7 @@
           <t>D | 484呎 (2房)
 $1386万
 $28,643/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -27731,7 +27731,7 @@
           <t>E | 499呎 (2房)
 $1419万
 $28,439/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -27762,7 +27762,7 @@
           <t>C | 546呎 (2房)
 $1566万
 $28,687/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -27770,7 +27770,7 @@
           <t>D | 484呎 (2房)
 $1381万
 $28,529/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -27778,7 +27778,7 @@
           <t>E | 499呎 (2房)
 $1413万
 $28,325/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
           <t>C | 546呎 (2房)
 $1560万
 $28,571/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -27817,7 +27817,7 @@
           <t>D | 484呎 (2房)
 $1375万
 $28,415/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -27825,7 +27825,7 @@
           <t>E | 499呎 (2房)
 $1408万
 $28,210/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -27856,7 +27856,7 @@
           <t>C | 546呎 (2房)
 $1554万
 $28,460/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -27864,7 +27864,7 @@
           <t>D | 484呎 (2房)
 $1370万
 $28,304/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -27903,7 +27903,7 @@
           <t>C | 546呎 (2房)
 $1623万
 $29,729/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -27911,7 +27911,7 @@
           <t>D | 484呎 (2房)
 $1364万
 $28,190/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -27919,7 +27919,7 @@
           <t>E | 499呎 (2房)
 $1397万
 $27,988/呎
-(26年-07月-10日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -27950,7 +27950,7 @@
           <t>C | 546呎 (2房)
 $1542万
 $28,233/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -27958,7 +27958,7 @@
           <t>D | 484呎 (2房)
 $1425万
 $29,446/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -27966,7 +27966,7 @@
           <t>E | 499呎 (2房)
 $1391万
 $27,878/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
           <t>C | 546呎 (2房)
 $1542万
 $28,233/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -28005,7 +28005,7 @@
           <t>D | 484呎 (2房)
 $1359万
 $28,076/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -28013,7 +28013,7 @@
           <t>E | 499呎 (2房)
 $1391万
 $27,878/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -28044,7 +28044,7 @@
           <t>C | 546呎 (2房)
 $1529万
 $28,011/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -28052,7 +28052,7 @@
           <t>D | 484呎 (2房)
 $1348万
 $27,853/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -28060,7 +28060,7 @@
           <t>E | 499呎 (2房)
 $1380万
 $27,655/呎
-(26年-07月-10日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -28091,7 +28091,7 @@
           <t>C | 546呎 (2房)
 $1523万
 $27,897/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -28099,7 +28099,7 @@
           <t>D | 484呎 (2房)
 $1343万
 $27,742/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -28107,7 +28107,7 @@
           <t>E | 499呎 (2房)
 $1374万
 $27,545/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -25888,7 +25888,7 @@
           <t>A | 1515呎 (4+房)
 $7367万
 $48,630/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25896,7 +25896,7 @@
           <t>B | 1154呎 (4+房)
 $5625万
 $48,745/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -25911,7 +25911,7 @@
           <t>A | 1515呎 (4+房)
 $7367万
 $48,630/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25919,7 +25919,7 @@
           <t>B | 1154呎 (4+房)
 $5625万
 $48,745/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -25957,7 +25957,7 @@
           <t>A | 1515呎 (4+房)
 $6832万
 $45,098/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25965,7 +25965,7 @@
           <t>B | 1154呎 (4+房)
 $5372万
 $46,553/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -25980,7 +25980,7 @@
           <t>A | 1515呎 (4+房)
 $6785万
 $44,787/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25988,7 +25988,7 @@
           <t>B | 1154呎 (4+房)
 $5335万
 $46,231/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -26003,7 +26003,7 @@
           <t>A | 1515呎 (4+房)
 $6801万
 $44,890/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26011,7 +26011,7 @@
           <t>B | 1154呎 (4+房)
 $5335万
 $46,231/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -26072,7 +26072,7 @@
           <t>A | 1515呎 (4+房)
 $6600万
 $43,562/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -26080,7 +26080,7 @@
           <t>B | 1154呎 (4+房)
 $5189万
 $44,967/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -26095,7 +26095,7 @@
           <t>A | 1515呎 (4+房)
 $6554万
 $43,260/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -26103,7 +26103,7 @@
           <t>B | 1154呎 (4+房)
 $5153万
 $44,657/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -26118,7 +26118,7 @@
           <t>A | 1450呎 (4+房)
 $6955万
 $47,968/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>A | 1450呎 (4+房)
 $6631万
 $45,728/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -26164,7 +26164,7 @@
           <t>A | 1450呎 (4+房)
 $6419万
 $44,267/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -26187,7 +26187,7 @@
           <t>A | 1515呎 (4+房)
 $6374万
 $42,074/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -26195,7 +26195,7 @@
           <t>B | 1154呎 (4+房)
 $5012万
 $43,434/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -26210,7 +26210,7 @@
           <t>A | 1515呎 (4+房)
 $6330万
 $41,783/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -26218,7 +26218,7 @@
           <t>B | 1154呎 (4+房)
 $4978万
 $43,134/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -26916,7 +26916,7 @@
           <t>C | 546呎 (2房)
 $1733万
 $31,747/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -26963,7 +26963,7 @@
           <t>C | 546呎 (2房)
 $1726万
 $31,621/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -26994,7 +26994,7 @@
           <t>A | 960呎 (3房)
 $4234万
 $44,102/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -27002,7 +27002,7 @@
           <t>B | 960呎 (3房)
 $4196万
 $43,709/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -27018,7 +27018,7 @@
           <t>D | 484呎 (2房)
 $1516万
 $31,322/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -27041,7 +27041,7 @@
           <t>A | 960呎 (3房)
 $4205万
 $43,798/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -27049,7 +27049,7 @@
           <t>B | 960呎 (3房)
 $4167万
 $43,406/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -27065,7 +27065,7 @@
           <t>D | 484呎 (2房)
 $1510万
 $31,196/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -27135,7 +27135,7 @@
           <t>A | 960呎 (3房)
 $3969万
 $41,342/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -27143,7 +27143,7 @@
           <t>B | 960呎 (3房)
 $3934万
 $40,974/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27182,7 +27182,7 @@
           <t>A | 960呎 (3房)
 $4099万
 $42,698/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -27190,7 +27190,7 @@
           <t>B | 960呎 (3房)
 $3906万
 $40,691/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -27229,7 +27229,7 @@
           <t>A | 960呎 (3房)
 $3941万
 $41,055/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -27237,7 +27237,7 @@
           <t>B | 960呎 (3房)
 $3906万
 $40,691/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -27339,7 +27339,7 @@
           <t>C | 546呎 (2房)
 $1624万
 $29,736/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -27370,7 +27370,7 @@
           <t>A | 960呎 (3房)
 $3834万
 $39,933/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -27378,7 +27378,7 @@
           <t>B | 960呎 (3房)
 $3800万
 $39,579/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -27386,7 +27386,7 @@
           <t>C | 546呎 (2房)
 $1617万
 $29,617/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -27417,7 +27417,7 @@
           <t>A | 960呎 (3房)
 $3807万
 $39,657/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -27425,7 +27425,7 @@
           <t>B | 960呎 (3房)
 $3773万
 $39,306/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -27433,7 +27433,7 @@
           <t>C | 546呎 (2房)
 $1611万
 $29,500/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -27464,7 +27464,7 @@
           <t>A | 960呎 (3房)
 $3874万
 $40,351/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -27480,7 +27480,7 @@
           <t>C | 546呎 (2房)
 $1604万
 $29,383/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -27511,7 +27511,7 @@
           <t>A | 960呎 (3房)
 $3847万
 $40,070/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -27519,7 +27519,7 @@
           <t>B | 960呎 (3房)
 $3813万
 $39,715/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -27527,7 +27527,7 @@
           <t>C | 546呎 (2房)
 $1598万
 $29,264/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -27535,7 +27535,7 @@
           <t>D | 484呎 (2房)
 $1409万
 $29,103/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -27543,7 +27543,7 @@
           <t>E | 499呎 (2房)
 $1442万
 $28,894/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27558,7 @@
           <t>A | 960呎 (3房)
 $3878万
 $40,395/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -27566,7 +27566,7 @@
           <t>B | 960呎 (3房)
 $3844万
 $40,036/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -27574,7 +27574,7 @@
           <t>C | 546呎 (2房)
 $1669万
 $30,570/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -27613,7 +27613,7 @@
           <t>B | 960呎 (3房)
 $3670万
 $38,230/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -27621,7 +27621,7 @@
           <t>C | 546呎 (2房)
 $1663万
 $30,449/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -27652,7 +27652,7 @@
           <t>A | 960呎 (3房)
 $3703万
 $38,573/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -27660,7 +27660,7 @@
           <t>B | 960呎 (3房)
 $3823万
 $39,824/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -27668,7 +27668,7 @@
           <t>C | 546呎 (2房)
 $1585万
 $29,033/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -27676,7 +27676,7 @@
           <t>D | 484呎 (2房)
 $1397万
 $28,872/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -27684,7 +27684,7 @@
           <t>E | 499呎 (2房)
 $1430万
 $28,665/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27715,7 @@
           <t>C | 546呎 (2房)
 $1573万
 $28,802/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -27723,7 +27723,7 @@
           <t>D | 484呎 (2房)
 $1386万
 $28,643/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -27731,7 +27731,7 @@
           <t>E | 499呎 (2房)
 $1419万
 $28,439/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -27762,7 +27762,7 @@
           <t>C | 546呎 (2房)
 $1566万
 $28,687/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -27770,7 +27770,7 @@
           <t>D | 484呎 (2房)
 $1381万
 $28,529/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -27778,7 +27778,7 @@
           <t>E | 499呎 (2房)
 $1413万
 $28,325/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
           <t>C | 546呎 (2房)
 $1560万
 $28,571/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -27817,7 +27817,7 @@
           <t>D | 484呎 (2房)
 $1375万
 $28,415/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -27825,7 +27825,7 @@
           <t>E | 499呎 (2房)
 $1408万
 $28,210/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -27856,7 +27856,7 @@
           <t>C | 546呎 (2房)
 $1554万
 $28,460/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -27864,7 +27864,7 @@
           <t>D | 484呎 (2房)
 $1370万
 $28,304/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -27903,7 +27903,7 @@
           <t>C | 546呎 (2房)
 $1623万
 $29,729/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -27911,7 +27911,7 @@
           <t>D | 484呎 (2房)
 $1364万
 $28,190/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -27919,7 +27919,7 @@
           <t>E | 499呎 (2房)
 $1397万
 $27,988/呎
-(26年-07月)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -27950,7 +27950,7 @@
           <t>C | 546呎 (2房)
 $1542万
 $28,233/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -27958,7 +27958,7 @@
           <t>D | 484呎 (2房)
 $1425万
 $29,446/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -27966,7 +27966,7 @@
           <t>E | 499呎 (2房)
 $1391万
 $27,878/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27997,7 @@
           <t>C | 546呎 (2房)
 $1542万
 $28,233/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -28005,7 +28005,7 @@
           <t>D | 484呎 (2房)
 $1359万
 $28,076/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -28013,7 +28013,7 @@
           <t>E | 499呎 (2房)
 $1391万
 $27,878/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -28044,7 +28044,7 @@
           <t>C | 546呎 (2房)
 $1529万
 $28,011/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -28052,7 +28052,7 @@
           <t>D | 484呎 (2房)
 $1348万
 $27,853/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -28060,7 +28060,7 @@
           <t>E | 499呎 (2房)
 $1380万
 $27,655/呎
-(26年-07月)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -28091,7 +28091,7 @@
           <t>C | 546呎 (2房)
 $1523万
 $27,897/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -28099,7 +28099,7 @@
           <t>D | 484呎 (2房)
 $1343万
 $27,742/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -28107,7 +28107,7 @@
           <t>E | 499呎 (2房)
 $1374万
 $27,545/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -8997,34 +8997,34 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>20803600</v>
+        <v>17059000</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>38102</v>
+        <v>31244</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="5" t="n">
-        <v>17058952</v>
+        <v>17059000</v>
       </c>
       <c r="L125" s="5" t="n">
         <v>31244</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -26525,7 +26525,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27099,12 +27099,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
-$2080万
-$38,102/呎
-(在售)</t>
+$1706万
+$31,244/呎
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
